--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.06098658913264</v>
+        <v>1.959910320734053</v>
       </c>
       <c r="D2" t="n">
-        <v>4.14797525884998</v>
+        <v>0.6740459795631218</v>
       </c>
       <c r="E2" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F2" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.018492825399929</v>
+        <v>0.3280050841274885</v>
       </c>
       <c r="D3" t="n">
-        <v>8.063684446668786</v>
+        <v>1.310348722583678</v>
       </c>
       <c r="E3" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F3" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.23570906903428</v>
+        <v>2.63830272371807</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62410047138672</v>
+        <v>3.188916326600343</v>
       </c>
       <c r="E4" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F4" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.8267783702258</v>
+        <v>2.571851485161692</v>
       </c>
       <c r="D5" t="n">
-        <v>10.31394096758361</v>
+        <v>1.676015407232336</v>
       </c>
       <c r="E5" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F5" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.25396298545316</v>
+        <v>1.991268985136138</v>
       </c>
       <c r="D6" t="n">
-        <v>20.81844022665409</v>
+        <v>3.38299653683129</v>
       </c>
       <c r="E6" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F6" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.46331661042689</v>
+        <v>3.000288949194369</v>
       </c>
       <c r="D7" t="n">
-        <v>9.400884408858341</v>
+        <v>1.52764371643948</v>
       </c>
       <c r="E7" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F7" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.618190278680832</v>
+        <v>1.075455920285635</v>
       </c>
       <c r="D8" t="n">
-        <v>24.68518695943445</v>
+        <v>4.011342880908098</v>
       </c>
       <c r="E8" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F8" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.14271558171884</v>
+        <v>1.973191282029312</v>
       </c>
       <c r="D9" t="n">
-        <v>7.823501208725704</v>
+        <v>1.271318946417927</v>
       </c>
       <c r="E9" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F9" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.27412951974457</v>
+        <v>3.619546046958493</v>
       </c>
       <c r="D10" t="n">
-        <v>27.25747136130848</v>
+        <v>4.429339096212628</v>
       </c>
       <c r="E10" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F10" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.24227752628779</v>
+        <v>2.314370098021766</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14514090644857</v>
+        <v>4.736085397297892</v>
       </c>
       <c r="E11" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F11" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.59023342126413</v>
+        <v>2.208412930955421</v>
       </c>
       <c r="D12" t="n">
-        <v>15.90860172174567</v>
+        <v>2.585147779783671</v>
       </c>
       <c r="E12" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F12" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.50600203066162</v>
+        <v>2.032225329982513</v>
       </c>
       <c r="D13" t="n">
-        <v>26.48077897875371</v>
+        <v>4.303126584047478</v>
       </c>
       <c r="E13" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F13" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.42204836809782</v>
+        <v>2.018582859815897</v>
       </c>
       <c r="D14" t="n">
-        <v>24.80682349066912</v>
+        <v>4.031108817233732</v>
       </c>
       <c r="E14" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F14" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.50575054264052</v>
+        <v>3.657184463179084</v>
       </c>
       <c r="D15" t="n">
-        <v>25.49475609176657</v>
+        <v>4.142897864912068</v>
       </c>
       <c r="E15" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F15" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.40956687459989</v>
+        <v>2.991554617122481</v>
       </c>
       <c r="D16" t="n">
-        <v>24.72399946326056</v>
+        <v>4.017649912779841</v>
       </c>
       <c r="E16" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F16" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.17650060159102</v>
+        <v>4.091181347758542</v>
       </c>
       <c r="D17" t="n">
-        <v>4.862496909782021</v>
+        <v>0.7901557478395785</v>
       </c>
       <c r="E17" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F17" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.12327812585793</v>
+        <v>7.982532695451914</v>
       </c>
       <c r="D18" t="n">
-        <v>47.16562823181528</v>
+        <v>7.664414587669983</v>
       </c>
       <c r="E18" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F18" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>28.76903960910578</v>
+        <v>4.67496893647969</v>
       </c>
       <c r="D19" t="n">
-        <v>7.645224534953845</v>
+        <v>1.24234898693</v>
       </c>
       <c r="E19" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F19" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>13.6672814275062</v>
+        <v>2.220933231969757</v>
       </c>
       <c r="D20" t="n">
-        <v>14.908256474555</v>
+        <v>2.422591677115187</v>
       </c>
       <c r="E20" t="n">
-        <v>9.663383707084799</v>
+        <v>1.57029985240128</v>
       </c>
       <c r="F20" t="n">
-        <v>10.63684592971458</v>
+        <v>1.728487463578619</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
